--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/IOWA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/IOWA_2019.xlsx
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C95">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C163">
@@ -9085,7 +9085,7 @@
         <v>24</v>
       </c>
       <c r="D485">
-        <v>0.009393346379647749</v>
+        <v>0.009393346379647748</v>
       </c>
     </row>
     <row r="486">
